--- a/Specification/battery_temp_control_design.xlsx
+++ b/Specification/battery_temp_control_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training\Specification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FBB22B-9824-437E-BF01-C2F5902E5A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5700F87D-A148-41F9-B5AA-159B8A83CF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="228">
   <si>
     <t>状態名</t>
   </si>
@@ -1642,10 +1642,13 @@
         <v>2</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>123</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.15">
@@ -1664,6 +1667,9 @@
       <c r="F5" s="3" t="s">
         <v>171</v>
       </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
@@ -1681,6 +1687,9 @@
       <c r="F6" s="3" t="s">
         <v>172</v>
       </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
@@ -1698,6 +1707,9 @@
       <c r="F7" s="3" t="s">
         <v>173</v>
       </c>
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
@@ -1715,6 +1727,9 @@
       <c r="F8" s="3" t="s">
         <v>174</v>
       </c>
+      <c r="G8" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
@@ -1732,6 +1747,9 @@
       <c r="F9" s="3" t="s">
         <v>175</v>
       </c>
+      <c r="G9" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
@@ -1748,6 +1766,9 @@
       </c>
       <c r="F10" s="3" t="s">
         <v>197</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">

--- a/Specification/battery_temp_control_design.xlsx
+++ b/Specification/battery_temp_control_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training\Specification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5700F87D-A148-41F9-B5AA-159B8A83CF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F26E6FC-FA29-49A2-8B78-7089B24A2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="231">
   <si>
     <t>状態名</t>
   </si>
@@ -1112,6 +1112,27 @@
   </si>
   <si>
     <t>セル異常フラグ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>温度制御状態</t>
+    <rPh sb="0" eb="2">
+      <t>オンド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>U8_Temperature_change_mode</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>温度変化モード(上昇、下降、維持)</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1808,10 +1829,14 @@
         <v>225</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
@@ -2283,7 +2308,9 @@
       <c r="H18" s="10">
         <v>10</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="12" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
@@ -2727,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
@@ -2817,6 +2844,14 @@
       </c>
       <c r="D9" s="3" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/Specification/battery_temp_control_design.xlsx
+++ b/Specification/battery_temp_control_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training\Specification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F26E6FC-FA29-49A2-8B78-7089B24A2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F31C49-6FEE-48C0-83F2-5B18B8B93FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="260">
   <si>
     <t>状態名</t>
   </si>
@@ -1133,6 +1133,99 @@
   </si>
   <si>
     <t>温度変化モード(上昇、下降、維持)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>simple-pid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  └─────────────┴────────────────────┴──────────────────────────────────────────────────────────────┘</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ┌──────────────┬─────┬────────────────────────────────────────────────────────────────────────────┐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  │ 名称         │ 型  │ 説明                                                                       │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ├──────────────┼─────┼────────────────────────────────────────────────────────────────────────────┤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  │ control /... │ flo │ current_value を setpoint に近づけるために、制御対象システムに適用すべ...  │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  └──────────────┴─────┴────────────────────────────────────────────────────────────────────────────┘</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>:---</t>
+  </si>
+  <si>
+    <t>`setpoint`</t>
+  </si>
+  <si>
+    <t>PIDコントローラが達成しようとする目標値。</t>
+  </si>
+  <si>
+    <t>`current_value`</t>
+  </si>
+  <si>
+    <t>制御対象システムから測定された現在の値。</t>
+  </si>
+  <si>
+    <t>`sample_time`</t>
+  </si>
+  <si>
+    <t>コントローラの更新間隔（秒）。</t>
+  </si>
+  <si>
+    <t>`output_limits`</t>
+  </si>
+  <si>
+    <t>。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>`Kp``Ki``Kd`</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>比例、積分、微分のゲイン。PIDオブジェクトの初期化時に設定します。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>tuple(float float)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">出力値を制約するためのタプル (min_output, max_output)。   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 名称 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 型 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 説明 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> :--- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `control` / `output` </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> float </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `current_value` を `setpoint`に近づけるために、制御対象システムに適用すべき計算された調整値。 </t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1216,7 +1309,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1232,6 +1325,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1278,7 +1377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1325,6 +1424,9 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1340,6 +1442,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>476707</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>66971</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29F16719-3D19-A05F-72FF-6894544CDB18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="6457950"/>
+          <a:ext cx="3277057" cy="2124371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2862,7 +3013,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
@@ -2870,16 +3021,18 @@
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>128</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>87</v>
       </c>
@@ -2895,8 +3048,21 @@
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I3" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+    </row>
+    <row r="4" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>91</v>
       </c>
@@ -2912,8 +3078,20 @@
       <c r="F4" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I4" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+    </row>
+    <row r="5" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2929,8 +3107,18 @@
       <c r="F5" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I5" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="N5" s="20"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
@@ -2946,8 +3134,20 @@
       <c r="F6" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I6" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
@@ -2963,8 +3163,20 @@
       <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I7" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+    </row>
+    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
         <v>98</v>
       </c>
@@ -2980,8 +3192,20 @@
       <c r="F8" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I8" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+    </row>
+    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
@@ -2997,8 +3221,19 @@
       <c r="F9" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I9" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="N9" s="20"/>
+    </row>
+    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -3014,8 +3249,14 @@
       <c r="F10" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B11" s="3" t="s">
         <v>106</v>
       </c>
@@ -3030,10 +3271,103 @@
       </c>
       <c r="F11" s="3" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="I12" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="M12" s="20"/>
+    </row>
+    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="I13" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="I14" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="M14" s="20"/>
+    </row>
+    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="B15" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+    </row>
+    <row r="24" spans="2:8" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="B24" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B29" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Specification/battery_temp_control_design.xlsx
+++ b/Specification/battery_temp_control_design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Training\Specification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F31C49-6FEE-48C0-83F2-5B18B8B93FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA71E6E9-AD69-40CA-8D2B-9721388F74ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21075" yWindow="-15870" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="258">
   <si>
     <t>状態名</t>
   </si>
@@ -37,21 +37,12 @@
     <t>説明</t>
   </si>
   <si>
-    <t>通常監視</t>
-  </si>
-  <si>
     <t>温度が範囲内、監視継続</t>
   </si>
   <si>
-    <t>高温制御</t>
-  </si>
-  <si>
     <t>高温 → 冷却制御へ</t>
   </si>
   <si>
-    <t>低温制御</t>
-  </si>
-  <si>
     <t>低温 → 加熱制御へ</t>
   </si>
   <si>
@@ -254,9 +245,6 @@
   </si>
   <si>
     <t>加熱制御</t>
-  </si>
-  <si>
-    <t>control_heater()</t>
   </si>
   <si>
     <t>ヒータ出力の調整</t>
@@ -695,35 +683,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>温度変化ディレイ時間</t>
-    <rPh sb="0" eb="2">
-      <t>オンド</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>安定温度に更新するときのインターバル時間</t>
-    <rPh sb="0" eb="2">
-      <t>アンテイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>オンド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>U16</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1226,6 +1185,22 @@
   </si>
   <si>
     <t xml:space="preserve"> `current_value` を `setpoint`に近づけるために、制御対象システムに適用すべき計算された調整値。 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>control_heater()</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通常監視</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>高温制御</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>低温制御</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1792,52 +1767,52 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -1845,19 +1820,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
@@ -1865,19 +1840,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -1885,19 +1860,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G8" s="3">
         <v>3</v>
@@ -1905,19 +1880,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E9" s="3">
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G9" s="3">
         <v>4</v>
@@ -1925,19 +1900,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3">
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G10" s="3">
         <v>5</v>
@@ -1945,43 +1920,43 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="J14" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1991,205 +1966,205 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B19" s="19" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F19" s="19"/>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B20" s="17" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F20" s="17"/>
     </row>
     <row r="21" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B21" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F21" s="17"/>
     </row>
     <row r="22" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B22" s="17" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F22" s="17"/>
     </row>
     <row r="23" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="17" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C23" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>208</v>
-      </c>
       <c r="E23" s="18" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F23" s="17"/>
     </row>
     <row r="24" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B24" s="17" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B25" s="17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F25" s="17"/>
     </row>
     <row r="26" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B26" s="17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F26" s="17"/>
     </row>
     <row r="27" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B27" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B28" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
     </row>
     <row r="29" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B29" s="17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B30" s="17" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B31" s="17" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2200,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -2213,66 +2188,66 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H4" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="G5" s="11">
         <v>0.01</v>
@@ -2281,39 +2256,39 @@
         <v>-40</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J5" s="11">
         <v>125</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="G6" s="10">
         <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J6" s="11">
         <v>125</v>
@@ -2322,25 +2297,25 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G7" s="10">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I7" s="10">
         <v>0</v>
@@ -2352,25 +2327,25 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I8" s="10" t="b">
         <v>0</v>
@@ -2382,25 +2357,25 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I9" s="10" t="b">
         <v>0</v>
@@ -2412,46 +2387,46 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G18" s="10">
         <v>1</v>
@@ -2460,22 +2435,22 @@
         <v>10</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E19" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="G19" s="10">
         <v>1</v>
@@ -2487,17 +2462,17 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="G20" s="10">
         <v>1</v>
@@ -2509,120 +2484,98 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="G21" s="10">
         <v>1</v>
       </c>
       <c r="H21" s="10">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E22" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="G22" s="10">
         <v>1</v>
       </c>
       <c r="H22" s="10">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="G23" s="10">
         <v>1</v>
       </c>
       <c r="H23" s="10">
-        <v>-20</v>
+        <v>85</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E24" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="G24" s="10">
         <v>1</v>
       </c>
       <c r="H24" s="10">
-        <v>85</v>
+        <v>-40</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B25" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1</v>
-      </c>
-      <c r="H25" s="10">
-        <v>-40</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2644,20 +2597,20 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
@@ -2666,61 +2619,61 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1"/>
     </row>
@@ -2742,20 +2695,20 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
@@ -2763,44 +2716,44 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2822,79 +2775,79 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B5" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B6" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2915,17 +2868,17 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B3" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>2</v>
@@ -2933,76 +2886,76 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>254</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="C13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3027,32 +2980,32 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K3" s="22" t="s">
         <v>2</v>
@@ -3064,28 +3017,28 @@
     </row>
     <row r="4" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20"/>
@@ -3093,55 +3046,55 @@
     </row>
     <row r="5" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N5" s="20"/>
     </row>
     <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
@@ -3149,28 +3102,28 @@
     </row>
     <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
@@ -3178,28 +3131,28 @@
     </row>
     <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="I8" s="21" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
@@ -3207,47 +3160,47 @@
     </row>
     <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="L9" s="20"/>
       <c r="N9" s="20"/>
     </row>
     <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
@@ -3258,60 +3211,60 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="I12" s="22" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="I13" s="21" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="M13" s="20"/>
     </row>
     <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="I14" s="21" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="M14" s="20"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -3321,7 +3274,7 @@
     </row>
     <row r="24" spans="2:8" ht="14.25" x14ac:dyDescent="0.15">
       <c r="B24" s="20" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -3332,37 +3285,37 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B33" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B34" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B35" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
